--- a/outputs/56599.xlsx
+++ b/outputs/56599.xlsx
@@ -114,12 +114,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -315,448 +319,448 @@
   <dimension ref="B2:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.56"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="str">
-        <f aca="false">IF(OR(M5="",M5&lt;G6,M5&gt;H30),"not found - please re-enter",VLOOKUP(M5,G$6:J$30,4,TRUE()))</f>
+      <c r="B2" s="1" t="str">
+        <f aca="false">IF(OR(M5="",M5&lt;G6,M5&gt;H30),"not found - please re-enter",INDEX(J6:J30,MATCH(M5,G6:G30,1)))</f>
         <v>not found - please re-enter</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>5871001</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <f aca="false">G6+9</f>
         <v>5871010</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1" t="n">
+      <c r="I6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2" t="n">
         <v>477101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <f aca="false">H6+1</f>
         <v>5871011</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <f aca="false">G7+9</f>
         <v>5871020</v>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="1" t="n">
+      <c r="I7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="2" t="n">
         <f aca="false">J6+1</f>
         <v>477102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <f aca="false">H7+1</f>
         <v>5871021</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <f aca="false">G8+9</f>
         <v>5871030</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="1" t="n">
+      <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="2" t="n">
         <f aca="false">J7+1</f>
         <v>477103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="2" t="n">
         <f aca="false">H8+1</f>
         <v>5871031</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <f aca="false">G9+9</f>
         <v>5871040</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1" t="n">
+      <c r="I9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="2" t="n">
         <f aca="false">J8+1</f>
         <v>477104</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="2" t="n">
         <f aca="false">H9+1</f>
         <v>5871041</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <f aca="false">G10+9</f>
         <v>5871050</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="1" t="n">
+      <c r="I10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" s="2" t="n">
         <f aca="false">J9+1</f>
         <v>477105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <f aca="false">H10+1</f>
         <v>5871051</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <f aca="false">G11+9</f>
         <v>5871060</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1" t="n">
+      <c r="I11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <f aca="false">J10+1</f>
         <v>477106</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="2" t="n">
         <f aca="false">H11+1</f>
         <v>5871061</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <f aca="false">G12+9</f>
         <v>5871070</v>
       </c>
-      <c r="I12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" s="1" t="n">
+      <c r="I12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="2" t="n">
         <f aca="false">J11+1</f>
         <v>477107</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="2" t="n">
         <f aca="false">H12+1</f>
         <v>5871071</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <f aca="false">G13+9</f>
         <v>5871080</v>
       </c>
-      <c r="I13" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1" t="n">
+      <c r="I13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="n">
         <f aca="false">J12+1</f>
         <v>477108</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="2" t="n">
         <f aca="false">H13+1</f>
         <v>5871081</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <f aca="false">G14+9</f>
         <v>5871090</v>
       </c>
-      <c r="I14" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="1" t="n">
+      <c r="I14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="2" t="n">
         <f aca="false">J13+1</f>
         <v>477109</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="2" t="n">
         <f aca="false">H14+1</f>
         <v>5871091</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <f aca="false">G15+9</f>
         <v>5871100</v>
       </c>
-      <c r="I15" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="1" t="n">
+      <c r="I15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="2" t="n">
         <f aca="false">J14+1</f>
         <v>477110</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="2" t="n">
         <f aca="false">H15+1</f>
         <v>5871101</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <f aca="false">G16+9</f>
         <v>5871110</v>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="1" t="n">
+      <c r="I16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="2" t="n">
         <f aca="false">J15+1</f>
         <v>477111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="2" t="n">
         <f aca="false">H16+1</f>
         <v>5871111</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="2" t="n">
         <f aca="false">G17+9</f>
         <v>5871120</v>
       </c>
-      <c r="I17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J17" s="1" t="n">
+      <c r="I17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="2" t="n">
         <f aca="false">J16+1</f>
         <v>477112</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="2" t="n">
         <f aca="false">H17+1</f>
         <v>5871121</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="2" t="n">
         <f aca="false">G18+9</f>
         <v>5871130</v>
       </c>
-      <c r="I18" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="1" t="n">
+      <c r="I18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="2" t="n">
         <f aca="false">J17+1</f>
         <v>477113</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="2" t="n">
         <f aca="false">H18+1</f>
         <v>5871131</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="2" t="n">
         <f aca="false">G19+9</f>
         <v>5871140</v>
       </c>
-      <c r="I19" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" s="1" t="n">
+      <c r="I19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="2" t="n">
         <f aca="false">J18+1</f>
         <v>477114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="2" t="n">
         <f aca="false">H19+1</f>
         <v>5871141</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="2" t="n">
         <f aca="false">G20+9</f>
         <v>5871150</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="1" t="n">
+      <c r="I20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="2" t="n">
         <f aca="false">J19+1</f>
         <v>477115</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="1" t="n">
+      <c r="G21" s="2" t="n">
         <f aca="false">H20+1</f>
         <v>5871151</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <f aca="false">G21+9</f>
         <v>5871160</v>
       </c>
-      <c r="I21" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="1" t="n">
+      <c r="I21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="2" t="n">
         <f aca="false">J20+1</f>
         <v>477116</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="2" t="n">
         <f aca="false">H21+1</f>
         <v>5871161</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="2" t="n">
         <f aca="false">G22+9</f>
         <v>5871170</v>
       </c>
-      <c r="I22" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="1" t="n">
+      <c r="I22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="2" t="n">
         <f aca="false">J21+1</f>
         <v>477117</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G23" s="1" t="n">
+      <c r="G23" s="2" t="n">
         <f aca="false">H22+1</f>
         <v>5871171</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="2" t="n">
         <f aca="false">G23+9</f>
         <v>5871180</v>
       </c>
-      <c r="I23" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J23" s="1" t="n">
+      <c r="I23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <f aca="false">J22+1</f>
         <v>477118</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G24" s="1" t="n">
+      <c r="G24" s="2" t="n">
         <f aca="false">H23+1</f>
         <v>5871181</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="2" t="n">
         <f aca="false">G24+9</f>
         <v>5871190</v>
       </c>
-      <c r="I24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="1" t="n">
+      <c r="I24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2" t="n">
         <f aca="false">J23+1</f>
         <v>477119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G25" s="1" t="n">
+      <c r="G25" s="2" t="n">
         <f aca="false">H24+1</f>
         <v>5871191</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="2" t="n">
         <f aca="false">G25+9</f>
         <v>5871200</v>
       </c>
-      <c r="I25" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="1" t="n">
+      <c r="I25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="2" t="n">
         <f aca="false">J24+1</f>
         <v>477120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G26" s="1" t="n">
+      <c r="G26" s="2" t="n">
         <f aca="false">H25+1</f>
         <v>5871201</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="2" t="n">
         <f aca="false">G26+9</f>
         <v>5871210</v>
       </c>
-      <c r="I26" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" s="1" t="n">
+      <c r="I26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <f aca="false">J25+1</f>
         <v>477121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G27" s="1" t="n">
+      <c r="G27" s="2" t="n">
         <f aca="false">H26+1</f>
         <v>5871211</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="2" t="n">
         <f aca="false">G27+9</f>
         <v>5871220</v>
       </c>
-      <c r="I27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="1" t="n">
+      <c r="I27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2" t="n">
         <f aca="false">J26+1</f>
         <v>477122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="1" t="n">
+      <c r="G28" s="2" t="n">
         <f aca="false">H27+1</f>
         <v>5871221</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="2" t="n">
         <f aca="false">G28+9</f>
         <v>5871230</v>
       </c>
-      <c r="I28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="1" t="n">
+      <c r="I28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <f aca="false">J27+1</f>
         <v>477123</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G29" s="1" t="n">
+      <c r="G29" s="2" t="n">
         <f aca="false">H28+1</f>
         <v>5871231</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="2" t="n">
         <f aca="false">G29+9</f>
         <v>5871240</v>
       </c>
-      <c r="I29" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" s="1" t="n">
+      <c r="I29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="2" t="n">
         <f aca="false">J28+1</f>
         <v>477124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G30" s="1" t="n">
+      <c r="G30" s="2" t="n">
         <f aca="false">H29+1</f>
         <v>5871241</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="2" t="n">
         <f aca="false">G30+9</f>
         <v>5871250</v>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="1" t="n">
+      <c r="I30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="2" t="n">
         <f aca="false">J29+1</f>
         <v>477125</v>
       </c>

--- a/outputs/56599.xlsx
+++ b/outputs/56599.xlsx
@@ -316,19 +316,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J30"/>
+  <dimension ref="B2:M30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.56"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="str">
-        <f aca="false">IF(OR(M5="",M5&lt;G6,M5&gt;H30),"not found - please re-enter",INDEX(J6:J30,MATCH(M5,G6:G30,1)))</f>
+        <f aca="false">IF(OR(M5="",M5="",ISBLANK(M5)),"not found - please re-enter",IFERROR(INDEX($J$6:$J$30,MATCH(M5,$G$6:$H$30,1)),"not found - please re-enter"))</f>
         <v>not found - please re-enter</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G5" s="2" t="s">
         <v>0</v>
       </c>
@@ -341,8 +341,9 @@
       <c r="J5" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G6" s="2" t="n">
         <v>5871001</v>
       </c>
@@ -357,7 +358,7 @@
         <v>477101</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G7" s="2" t="n">
         <f aca="false">H6+1</f>
         <v>5871011</v>
@@ -374,7 +375,7 @@
         <v>477102</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G8" s="2" t="n">
         <f aca="false">H7+1</f>
         <v>5871021</v>
@@ -391,7 +392,7 @@
         <v>477103</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G9" s="2" t="n">
         <f aca="false">H8+1</f>
         <v>5871031</v>
@@ -408,7 +409,7 @@
         <v>477104</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G10" s="2" t="n">
         <f aca="false">H9+1</f>
         <v>5871041</v>
@@ -425,7 +426,7 @@
         <v>477105</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G11" s="2" t="n">
         <f aca="false">H10+1</f>
         <v>5871051</v>
@@ -442,7 +443,7 @@
         <v>477106</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G12" s="2" t="n">
         <f aca="false">H11+1</f>
         <v>5871061</v>
@@ -459,7 +460,7 @@
         <v>477107</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G13" s="2" t="n">
         <f aca="false">H12+1</f>
         <v>5871071</v>
@@ -476,7 +477,7 @@
         <v>477108</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G14" s="2" t="n">
         <f aca="false">H13+1</f>
         <v>5871081</v>
@@ -493,7 +494,7 @@
         <v>477109</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G15" s="2" t="n">
         <f aca="false">H14+1</f>
         <v>5871091</v>
@@ -510,7 +511,7 @@
         <v>477110</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G16" s="2" t="n">
         <f aca="false">H15+1</f>
         <v>5871101</v>
@@ -527,7 +528,7 @@
         <v>477111</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G17" s="2" t="n">
         <f aca="false">H16+1</f>
         <v>5871111</v>
@@ -544,7 +545,7 @@
         <v>477112</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G18" s="2" t="n">
         <f aca="false">H17+1</f>
         <v>5871121</v>
@@ -561,7 +562,7 @@
         <v>477113</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G19" s="2" t="n">
         <f aca="false">H18+1</f>
         <v>5871131</v>
@@ -578,7 +579,7 @@
         <v>477114</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G20" s="2" t="n">
         <f aca="false">H19+1</f>
         <v>5871141</v>
@@ -595,7 +596,7 @@
         <v>477115</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G21" s="2" t="n">
         <f aca="false">H20+1</f>
         <v>5871151</v>
@@ -612,7 +613,7 @@
         <v>477116</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G22" s="2" t="n">
         <f aca="false">H21+1</f>
         <v>5871161</v>
@@ -629,7 +630,7 @@
         <v>477117</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G23" s="2" t="n">
         <f aca="false">H22+1</f>
         <v>5871171</v>
@@ -646,7 +647,7 @@
         <v>477118</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G24" s="2" t="n">
         <f aca="false">H23+1</f>
         <v>5871181</v>
@@ -663,7 +664,7 @@
         <v>477119</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G25" s="2" t="n">
         <f aca="false">H24+1</f>
         <v>5871191</v>
@@ -680,7 +681,7 @@
         <v>477120</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G26" s="2" t="n">
         <f aca="false">H25+1</f>
         <v>5871201</v>
@@ -697,7 +698,7 @@
         <v>477121</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G27" s="2" t="n">
         <f aca="false">H26+1</f>
         <v>5871211</v>
@@ -714,7 +715,7 @@
         <v>477122</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G28" s="2" t="n">
         <f aca="false">H27+1</f>
         <v>5871221</v>
@@ -731,7 +732,7 @@
         <v>477123</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G29" s="2" t="n">
         <f aca="false">H28+1</f>
         <v>5871231</v>
@@ -748,7 +749,7 @@
         <v>477124</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G30" s="2" t="n">
         <f aca="false">H29+1</f>
         <v>5871241</v>
